--- a/E楼交接班容量报表空模板.xlsx
+++ b/E楼交接班容量报表空模板.xlsx
@@ -4856,7 +4856,10 @@
       <c r="AB29" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="AC29" s="82"/>
+      <c r="AC29" s="82">
+        <f>(AC26+AC28)*2.25*2.25*3.14</f>
+        <v>0</v>
+      </c>
       <c r="AD29" s="70"/>
       <c r="AE29" s="71"/>
     </row>
@@ -13714,7 +13717,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f8ab2b8-659f-42b3-854b-70a2b9081432}</x14:id>
+          <x14:id>{e947d0d4-7b76-4510-8e78-019bc976b483}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13726,7 +13729,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e103004c-c4e4-4fa3-9769-fb9ca26f4c78}</x14:id>
+          <x14:id>{c44d24f2-b2b0-406c-bb45-edb0fa89259b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13738,7 +13741,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49e3769f-6f5d-4eec-8ee3-f9c3803651a0}</x14:id>
+          <x14:id>{4cb7dd89-7b07-437d-a95f-66dd2140c3e2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13750,7 +13753,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1fbfc07f-79a1-4135-9d97-62d943420f52}</x14:id>
+          <x14:id>{98168f69-cfb3-4676-9ba3-c9bfb6114326}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13762,7 +13765,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b70d59b5-a2ab-42bb-b40e-2fcafc450e49}</x14:id>
+          <x14:id>{8ce8d1e6-9186-4228-a88a-afcee15934d7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13774,7 +13777,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b958743-889b-4872-9d75-95ff8da8b1c3}</x14:id>
+          <x14:id>{253a9f5a-01e8-4e5f-8445-0dfa8c107695}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13786,7 +13789,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cfab5dfe-0060-4c26-9875-9b1d70ee3b06}</x14:id>
+          <x14:id>{be3ea5a1-349d-4046-9c10-a032bc82560d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13798,7 +13801,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8f749d85-1abd-47cd-b97e-8ead994726be}</x14:id>
+          <x14:id>{7dd4fd26-61a8-4251-9f5c-74be96a9e26d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13812,7 +13815,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{132bcd4b-2115-4e4a-8f1e-1658d3f7d11e}</x14:id>
+          <x14:id>{f7ff0b80-392b-418e-bc97-07a709feb426}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13824,7 +13827,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f001f1c8-2884-4540-ba0e-e1ee630b7f8c}</x14:id>
+          <x14:id>{90be067f-6bec-4397-a450-10633d82c5d8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13836,7 +13839,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba64f036-3945-41af-9e2a-d87ebeaab8d7}</x14:id>
+          <x14:id>{ec97776d-eb38-4567-99b7-98689d7eb5cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13848,7 +13851,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd370852-24d3-47b4-a3b4-decff3c2be3d}</x14:id>
+          <x14:id>{841a89ad-594b-4e7f-a502-fe7bad49cbb9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13860,7 +13863,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b5cf09fb-9cea-486b-8e81-dc15c4b1761b}</x14:id>
+          <x14:id>{cff10fb1-fb22-46d3-a3da-8dfdc6376924}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13872,7 +13875,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2759981-a8e1-4a96-acfa-f05c94cca9a8}</x14:id>
+          <x14:id>{f5a6c382-1f77-422e-8181-ab3dce06f7b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13884,7 +13887,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d68aae1-86d7-4e6e-a625-5b431a243431}</x14:id>
+          <x14:id>{43e77d16-7cc5-4496-ad52-7d142e11889b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13896,7 +13899,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8fefc0ff-7559-471f-bdfb-92614b8b819d}</x14:id>
+          <x14:id>{51cfee5d-7962-4318-8ae4-b8aa3bec4749}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13910,7 +13913,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{724a13fe-4e2f-4eeb-a221-a4c34f6ac784}</x14:id>
+          <x14:id>{410396c6-637f-44c8-8d40-74dda37cf10c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13922,7 +13925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f42d3815-2df8-47a2-aecb-a2e7a83cad31}</x14:id>
+          <x14:id>{0e66eeaf-e933-450e-90f3-a410d0b0015d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13934,7 +13937,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1348c56d-ac9e-4c15-9611-f4100572a72f}</x14:id>
+          <x14:id>{0dfe22bc-7faf-4736-892a-16ba07cdddef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13946,7 +13949,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1822f730-b14b-4cdf-bbd9-fccb42829e5a}</x14:id>
+          <x14:id>{f8999872-9f58-4b14-a571-661dcf30e740}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13958,7 +13961,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc5684ee-1bd5-493c-bbf6-aea4718a9239}</x14:id>
+          <x14:id>{b8a7c6b3-a8c7-4dc0-ba90-8e30888cb74e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13970,7 +13973,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f8c8e042-16cc-4cb4-9b3c-2043324e5161}</x14:id>
+          <x14:id>{b3b1ad42-64f5-4adc-8c62-8b21d18b35d8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13982,7 +13985,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e31d3fc-5aac-4fca-ab79-c4172e740a56}</x14:id>
+          <x14:id>{5bab459e-9ae8-4bf4-93ac-aef23f956b0d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13994,7 +13997,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{058a43bb-134c-4fd5-a962-56bae87b932c}</x14:id>
+          <x14:id>{fedcb5c3-737f-428b-93b2-91316a16b576}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14008,7 +14011,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{95671c19-f6e2-4d14-989e-89b03b15aab4}</x14:id>
+          <x14:id>{d41c6b00-fa80-439b-9756-bbb9eb993f31}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14020,7 +14023,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e502c1c3-e1b9-472a-99ee-ee888f3c3fa0}</x14:id>
+          <x14:id>{180b57c8-bd92-4e57-b2e8-4882e3e820a9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14032,7 +14035,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{972b201a-0d09-4cc3-8b10-003409a0a2a0}</x14:id>
+          <x14:id>{348dc099-ada8-499e-8b89-7bd32e6e2b03}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14044,7 +14047,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{06570661-22df-4640-b7e3-5cbd80ffce32}</x14:id>
+          <x14:id>{ba97ccdb-e2aa-479a-a051-d5e6bf68a860}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14056,7 +14059,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e937705d-3735-473f-ae16-8850ba221086}</x14:id>
+          <x14:id>{1bb0687b-5e5c-4f7c-9f29-c22a703eb835}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14068,7 +14071,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27e00057-c2ac-49ba-aa9d-57ab209071fd}</x14:id>
+          <x14:id>{9e4c806f-75f7-4523-a1ad-dea2e862ced9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14080,7 +14083,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9fdc44a5-fddb-4b90-bcc8-6dad20809652}</x14:id>
+          <x14:id>{486634cc-68e7-47f3-b675-11e5ab941806}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14092,7 +14095,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c943b295-da13-4990-83ff-95f20ebdf311}</x14:id>
+          <x14:id>{77469f85-4b97-4a10-8dfe-fac5e6440bf9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14106,7 +14109,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{45c45535-357f-4fe7-8287-34be560e5818}</x14:id>
+          <x14:id>{ecec7b35-de13-4741-a844-64ef1f84034c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14118,7 +14121,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0301ef99-2cd9-4460-924c-4d734d236d6b}</x14:id>
+          <x14:id>{8acb57b0-de4e-4be2-ac29-c85194bb0207}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14130,7 +14133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{835f3940-de3b-4c74-af91-fb784c82fd98}</x14:id>
+          <x14:id>{b54a52be-8088-463c-bf61-50d32e8054a5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14142,7 +14145,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f0311d9-ac86-4bf8-880c-c4d4084371be}</x14:id>
+          <x14:id>{e30c9ab2-ca01-460f-9b70-5ceb09861a5b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14154,7 +14157,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac5725b4-2aac-4861-9a22-76749211c59c}</x14:id>
+          <x14:id>{a6f50170-f74d-4e6d-af8b-0b889910ef49}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14166,7 +14169,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4edc7fb0-4b09-49dd-9b3f-aea5c9eea3ae}</x14:id>
+          <x14:id>{5c1991c1-6656-405f-8afd-bae7d965d043}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14178,7 +14181,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{33b1d2fd-2c41-45f0-aaa2-54b950563956}</x14:id>
+          <x14:id>{1ddd8f47-f46a-43f1-9ccf-02b56131a8f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14190,7 +14193,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8b1177c4-e07d-4bf2-9a07-ecdacff48c38}</x14:id>
+          <x14:id>{d8a6de4a-4c23-421c-a737-fa0457962359}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14204,7 +14207,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6378e9c4-dc21-44de-bca8-5b500886d24e}</x14:id>
+          <x14:id>{c6412cee-d127-4f99-b35f-bce9b0c1f456}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14216,7 +14219,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{492fbdeb-2f99-4592-98c8-01015a152b08}</x14:id>
+          <x14:id>{53393c4d-992a-428a-af56-9ccf59533dc5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14228,7 +14231,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4b2ebd09-69d2-4f00-890b-95824ddc1979}</x14:id>
+          <x14:id>{22690656-df3d-4a1d-9254-2481318311ed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14240,7 +14243,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3f9dfcb6-5eff-4dad-8253-d53526e2b38e}</x14:id>
+          <x14:id>{31386eb4-3fe6-4ac3-b4ca-c5cb78e482af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14252,7 +14255,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c69c651d-5404-491d-aee8-4b95d50ba9e5}</x14:id>
+          <x14:id>{46b71828-fcc3-4306-b8ee-7c707ccac79b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14264,7 +14267,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4b2689c9-e890-44ed-94fb-f381bcc7af4f}</x14:id>
+          <x14:id>{f7713b7b-aa68-4bdb-957d-3347b51abb0b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14276,7 +14279,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e0173ed5-c078-42e0-a379-cf382d2e5257}</x14:id>
+          <x14:id>{e84d9e76-e88d-4c96-8d71-8b07e6351517}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14288,7 +14291,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65cc7cf5-14c0-4b5f-811f-ca1b8efbbbd6}</x14:id>
+          <x14:id>{359dbfec-4a6c-40e0-ae76-2bb1f799150b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14302,7 +14305,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d4b99512-e121-4139-bf4f-478598f3b8ed}</x14:id>
+          <x14:id>{949907f8-4e5c-4f63-b0b4-7f0ee70501df}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14314,7 +14317,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7990eb3-e2a8-4729-9627-76a9d283c86b}</x14:id>
+          <x14:id>{6f92c482-7162-48e9-9c4d-24b6585ae2ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14326,7 +14329,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75d7fee4-819b-44d9-8b20-6a7c4d59367a}</x14:id>
+          <x14:id>{77a4be30-fb90-4bb1-9e17-6ff215ab8dd2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14338,7 +14341,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bf167ec8-97f8-4a4f-ba88-8c79cb10fc18}</x14:id>
+          <x14:id>{2ae61df5-24dc-4007-8682-ca1b39fc4457}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14350,7 +14353,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39c6f328-e21c-487e-9581-bddc8a5f186d}</x14:id>
+          <x14:id>{e218c815-f620-4ab9-b2c1-c619e5672944}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14362,7 +14365,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3c70eec-574d-4356-a558-48c9608afde4}</x14:id>
+          <x14:id>{48bb6745-e35a-4ac4-8113-3e4b2199b3e7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14374,7 +14377,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{021101b6-8b46-487c-b045-56b47db6efe3}</x14:id>
+          <x14:id>{59f633d6-7aee-47fb-a523-11c281ebe6f4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14386,7 +14389,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{454fa8b0-dc96-45a7-9abf-4fe778497fd0}</x14:id>
+          <x14:id>{49f06d25-c74f-43ff-9142-1acd8553f4e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14400,7 +14403,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{660c922d-c322-4e1f-8fb1-db4774b5108c}</x14:id>
+          <x14:id>{45f5d649-00d2-4773-a3e7-bc4d5f60ef11}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14414,7 +14417,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ae039ae-cfd2-4723-806c-aa9965162f54}</x14:id>
+          <x14:id>{0dede596-0dc9-4b96-a014-2eefbd147335}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14428,7 +14431,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2669753b-ea0b-452e-8989-626ec7c7b8bd}</x14:id>
+          <x14:id>{f0516f3b-8c3c-44c2-b167-5a93f6df5fd0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14442,7 +14445,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e19dd18-97db-4fd5-8e86-0653719ff076}</x14:id>
+          <x14:id>{64368faf-b4e7-461e-af1c-dfeeaf325e31}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14454,7 +14457,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b018b58-33a7-48ff-9aec-861c382930c1}</x14:id>
+          <x14:id>{1de019e6-1729-48d5-9d12-b75b1dd4f460}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14466,7 +14469,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3294e00-1e6c-4312-824c-622cd3063868}</x14:id>
+          <x14:id>{b504a1b0-d920-4a9f-abb6-7a720dd12403}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14478,7 +14481,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4dedcafa-b9ff-4bf4-b4eb-8fa8b925331c}</x14:id>
+          <x14:id>{cb764419-424c-4940-b947-4ec850a2b856}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14490,7 +14493,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d117c7c5-2c2b-4130-b77b-b6d2b8bd77a4}</x14:id>
+          <x14:id>{1c062047-08b2-41e7-868a-6b474c0ee37d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14502,7 +14505,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eaecd9f0-0e92-426c-82df-369973eb2a9e}</x14:id>
+          <x14:id>{a3d88865-884d-47ad-b66b-474372e20f86}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14514,7 +14517,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d842f337-be2b-4ddd-aec6-41cd66fa1536}</x14:id>
+          <x14:id>{4884e0e4-e743-4ffc-bde7-844d246bc152}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14526,7 +14529,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b6816a42-ff2a-4f11-beb0-6f2a8e77605d}</x14:id>
+          <x14:id>{2e1b558b-473a-4472-8f54-ca32e7bb6c5c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14540,7 +14543,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{44ab21ed-40fd-4816-b690-93c0ce8ede0a}</x14:id>
+          <x14:id>{dd8e2e00-de06-45e3-9b2b-a57aea4e269b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14552,7 +14555,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f762d2f-bcfb-44e4-9975-728c71e7802a}</x14:id>
+          <x14:id>{c7e8d78f-65c5-454d-9eaf-03c1a14b3eef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14566,7 +14569,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af3dccdd-07f0-40c8-83ea-21a3fee232b0}</x14:id>
+          <x14:id>{0ae70342-011e-4ad3-b967-dc71d675d58e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14580,7 +14583,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7b110bb-9790-4d0d-8139-140a818cffdb}</x14:id>
+          <x14:id>{d211ee09-d714-45db-af85-1433cf06cd07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14592,7 +14595,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5ba520d9-c72b-4e5f-86e8-bba8b29380f5}</x14:id>
+          <x14:id>{8485f837-5657-4eda-981f-97407c1c2f57}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14606,7 +14609,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{da491c53-d03c-4bf2-b9ef-9823ffd28842}</x14:id>
+          <x14:id>{2f9c079a-1998-49b6-afe6-044c4ccc6f9f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14618,7 +14621,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13738b4b-240a-488f-b083-178f2b5e040c}</x14:id>
+          <x14:id>{7d0009a4-dc70-4ead-885b-d95e41d1d924}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14632,7 +14635,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba0c5448-d32a-4675-9089-76b81e755493}</x14:id>
+          <x14:id>{48bc4bd8-674b-40cb-b6d8-52024244c8bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14646,7 +14649,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8f451540-f630-4265-bc19-82120acc6706}</x14:id>
+          <x14:id>{60051a04-10f0-442d-999a-e9ae5310da52}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14658,7 +14661,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17181710-2ecf-4e19-93a6-ef82998c0bfa}</x14:id>
+          <x14:id>{7144b85d-6e20-45dc-a107-a255a0033856}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14672,7 +14675,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fd8c2d4f-9ca3-4f1a-b1b0-d72889cc5208}</x14:id>
+          <x14:id>{1208efef-11e3-4705-b89e-b066356f6415}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14686,7 +14689,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{76a5327a-5948-46e7-9077-382bdfd2f832}</x14:id>
+          <x14:id>{9c26a5c8-58da-4fa6-9cad-f76bb37201a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14698,7 +14701,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{47b64aed-da21-47f3-9440-c77a8fc347b9}</x14:id>
+          <x14:id>{01c24f63-9d3c-4c0d-bee5-4ddb336a725b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14710,7 +14713,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{581c8166-3232-4450-85b6-505e48de7565}</x14:id>
+          <x14:id>{dcb0dba8-1b04-4f3e-9b75-5d668b30cde2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14724,7 +14727,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{407d13e1-aff9-41d1-8dc7-a8428c93ebec}</x14:id>
+          <x14:id>{1d130f01-ad99-4a14-a80c-c5945538fe3a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14736,7 +14739,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1d7204ba-4c9e-42e0-b4cc-31eadfa107ab}</x14:id>
+          <x14:id>{cdcfa7eb-837d-4eda-8489-80e85184b478}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14748,7 +14751,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fc2afdd3-dc76-469e-9597-311e18cdc97b}</x14:id>
+          <x14:id>{cd0b5d2e-333e-492d-b723-3a8de40cd710}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14762,7 +14765,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9fcb19b0-7885-49b2-b8e5-84a1f0c644d0}</x14:id>
+          <x14:id>{bb528e2a-aadb-4970-9798-264f351520d8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14774,7 +14777,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62bf14c4-f22e-4706-aca6-3c89b91e71e1}</x14:id>
+          <x14:id>{c7ea6d54-2346-4a52-9b46-ee3ddc87ccfd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14811,7 +14814,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2f8ab2b8-659f-42b3-854b-70a2b9081432}">
+          <x14:cfRule type="dataBar" id="{e947d0d4-7b76-4510-8e78-019bc976b483}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14822,7 +14825,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e103004c-c4e4-4fa3-9769-fb9ca26f4c78}">
+          <x14:cfRule type="dataBar" id="{c44d24f2-b2b0-406c-bb45-edb0fa89259b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14833,14 +14836,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{49e3769f-6f5d-4eec-8ee3-f9c3803651a0}">
+          <x14:cfRule type="dataBar" id="{4cb7dd89-7b07-437d-a95f-66dd2140c3e2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1fbfc07f-79a1-4135-9d97-62d943420f52}">
+          <x14:cfRule type="dataBar" id="{98168f69-cfb3-4676-9ba3-c9bfb6114326}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14851,7 +14854,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b70d59b5-a2ab-42bb-b40e-2fcafc450e49}">
+          <x14:cfRule type="dataBar" id="{8ce8d1e6-9186-4228-a88a-afcee15934d7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14862,7 +14865,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1b958743-889b-4872-9d75-95ff8da8b1c3}">
+          <x14:cfRule type="dataBar" id="{253a9f5a-01e8-4e5f-8445-0dfa8c107695}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14873,7 +14876,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cfab5dfe-0060-4c26-9875-9b1d70ee3b06}">
+          <x14:cfRule type="dataBar" id="{be3ea5a1-349d-4046-9c10-a032bc82560d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14882,7 +14885,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8f749d85-1abd-47cd-b97e-8ead994726be}">
+          <x14:cfRule type="dataBar" id="{7dd4fd26-61a8-4251-9f5c-74be96a9e26d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14894,7 +14897,7 @@
           <xm:sqref>AD56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{132bcd4b-2115-4e4a-8f1e-1658d3f7d11e}">
+          <x14:cfRule type="dataBar" id="{f7ff0b80-392b-418e-bc97-07a709feb426}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14905,7 +14908,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f001f1c8-2884-4540-ba0e-e1ee630b7f8c}">
+          <x14:cfRule type="dataBar" id="{90be067f-6bec-4397-a450-10633d82c5d8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14916,14 +14919,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ba64f036-3945-41af-9e2a-d87ebeaab8d7}">
+          <x14:cfRule type="dataBar" id="{ec97776d-eb38-4567-99b7-98689d7eb5cd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dd370852-24d3-47b4-a3b4-decff3c2be3d}">
+          <x14:cfRule type="dataBar" id="{841a89ad-594b-4e7f-a502-fe7bad49cbb9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14934,7 +14937,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b5cf09fb-9cea-486b-8e81-dc15c4b1761b}">
+          <x14:cfRule type="dataBar" id="{cff10fb1-fb22-46d3-a3da-8dfdc6376924}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14945,7 +14948,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b2759981-a8e1-4a96-acfa-f05c94cca9a8}">
+          <x14:cfRule type="dataBar" id="{f5a6c382-1f77-422e-8181-ab3dce06f7b6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14956,7 +14959,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8d68aae1-86d7-4e6e-a625-5b431a243431}">
+          <x14:cfRule type="dataBar" id="{43e77d16-7cc5-4496-ad52-7d142e11889b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14965,7 +14968,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8fefc0ff-7559-471f-bdfb-92614b8b819d}">
+          <x14:cfRule type="dataBar" id="{51cfee5d-7962-4318-8ae4-b8aa3bec4749}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14977,7 +14980,7 @@
           <xm:sqref>K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{724a13fe-4e2f-4eeb-a221-a4c34f6ac784}">
+          <x14:cfRule type="dataBar" id="{410396c6-637f-44c8-8d40-74dda37cf10c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14988,7 +14991,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f42d3815-2df8-47a2-aecb-a2e7a83cad31}">
+          <x14:cfRule type="dataBar" id="{0e66eeaf-e933-450e-90f3-a410d0b0015d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14999,14 +15002,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1348c56d-ac9e-4c15-9611-f4100572a72f}">
+          <x14:cfRule type="dataBar" id="{0dfe22bc-7faf-4736-892a-16ba07cdddef}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1822f730-b14b-4cdf-bbd9-fccb42829e5a}">
+          <x14:cfRule type="dataBar" id="{f8999872-9f58-4b14-a571-661dcf30e740}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15017,7 +15020,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dc5684ee-1bd5-493c-bbf6-aea4718a9239}">
+          <x14:cfRule type="dataBar" id="{b8a7c6b3-a8c7-4dc0-ba90-8e30888cb74e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15028,7 +15031,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f8c8e042-16cc-4cb4-9b3c-2043324e5161}">
+          <x14:cfRule type="dataBar" id="{b3b1ad42-64f5-4adc-8c62-8b21d18b35d8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15039,7 +15042,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9e31d3fc-5aac-4fca-ab79-c4172e740a56}">
+          <x14:cfRule type="dataBar" id="{5bab459e-9ae8-4bf4-93ac-aef23f956b0d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15048,7 +15051,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{058a43bb-134c-4fd5-a962-56bae87b932c}">
+          <x14:cfRule type="dataBar" id="{fedcb5c3-737f-428b-93b2-91316a16b576}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15060,7 +15063,7 @@
           <xm:sqref>AD60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{95671c19-f6e2-4d14-989e-89b03b15aab4}">
+          <x14:cfRule type="dataBar" id="{d41c6b00-fa80-439b-9756-bbb9eb993f31}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15071,7 +15074,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e502c1c3-e1b9-472a-99ee-ee888f3c3fa0}">
+          <x14:cfRule type="dataBar" id="{180b57c8-bd92-4e57-b2e8-4882e3e820a9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15082,14 +15085,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{972b201a-0d09-4cc3-8b10-003409a0a2a0}">
+          <x14:cfRule type="dataBar" id="{348dc099-ada8-499e-8b89-7bd32e6e2b03}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{06570661-22df-4640-b7e3-5cbd80ffce32}">
+          <x14:cfRule type="dataBar" id="{ba97ccdb-e2aa-479a-a051-d5e6bf68a860}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15100,7 +15103,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e937705d-3735-473f-ae16-8850ba221086}">
+          <x14:cfRule type="dataBar" id="{1bb0687b-5e5c-4f7c-9f29-c22a703eb835}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15111,7 +15114,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{27e00057-c2ac-49ba-aa9d-57ab209071fd}">
+          <x14:cfRule type="dataBar" id="{9e4c806f-75f7-4523-a1ad-dea2e862ced9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15122,7 +15125,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9fdc44a5-fddb-4b90-bcc8-6dad20809652}">
+          <x14:cfRule type="dataBar" id="{486634cc-68e7-47f3-b675-11e5ab941806}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15131,7 +15134,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c943b295-da13-4990-83ff-95f20ebdf311}">
+          <x14:cfRule type="dataBar" id="{77469f85-4b97-4a10-8dfe-fac5e6440bf9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15143,7 +15146,7 @@
           <xm:sqref>K61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{45c45535-357f-4fe7-8287-34be560e5818}">
+          <x14:cfRule type="dataBar" id="{ecec7b35-de13-4741-a844-64ef1f84034c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15154,7 +15157,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0301ef99-2cd9-4460-924c-4d734d236d6b}">
+          <x14:cfRule type="dataBar" id="{8acb57b0-de4e-4be2-ac29-c85194bb0207}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15165,14 +15168,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{835f3940-de3b-4c74-af91-fb784c82fd98}">
+          <x14:cfRule type="dataBar" id="{b54a52be-8088-463c-bf61-50d32e8054a5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6f0311d9-ac86-4bf8-880c-c4d4084371be}">
+          <x14:cfRule type="dataBar" id="{e30c9ab2-ca01-460f-9b70-5ceb09861a5b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15183,7 +15186,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ac5725b4-2aac-4861-9a22-76749211c59c}">
+          <x14:cfRule type="dataBar" id="{a6f50170-f74d-4e6d-af8b-0b889910ef49}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15194,7 +15197,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4edc7fb0-4b09-49dd-9b3f-aea5c9eea3ae}">
+          <x14:cfRule type="dataBar" id="{5c1991c1-6656-405f-8afd-bae7d965d043}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15205,7 +15208,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{33b1d2fd-2c41-45f0-aaa2-54b950563956}">
+          <x14:cfRule type="dataBar" id="{1ddd8f47-f46a-43f1-9ccf-02b56131a8f6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15214,7 +15217,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8b1177c4-e07d-4bf2-9a07-ecdacff48c38}">
+          <x14:cfRule type="dataBar" id="{d8a6de4a-4c23-421c-a737-fa0457962359}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15226,7 +15229,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6378e9c4-dc21-44de-bca8-5b500886d24e}">
+          <x14:cfRule type="dataBar" id="{c6412cee-d127-4f99-b35f-bce9b0c1f456}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15237,7 +15240,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{492fbdeb-2f99-4592-98c8-01015a152b08}">
+          <x14:cfRule type="dataBar" id="{53393c4d-992a-428a-af56-9ccf59533dc5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15248,14 +15251,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4b2ebd09-69d2-4f00-890b-95824ddc1979}">
+          <x14:cfRule type="dataBar" id="{22690656-df3d-4a1d-9254-2481318311ed}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3f9dfcb6-5eff-4dad-8253-d53526e2b38e}">
+          <x14:cfRule type="dataBar" id="{31386eb4-3fe6-4ac3-b4ca-c5cb78e482af}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15266,7 +15269,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c69c651d-5404-491d-aee8-4b95d50ba9e5}">
+          <x14:cfRule type="dataBar" id="{46b71828-fcc3-4306-b8ee-7c707ccac79b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15277,7 +15280,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4b2689c9-e890-44ed-94fb-f381bcc7af4f}">
+          <x14:cfRule type="dataBar" id="{f7713b7b-aa68-4bdb-957d-3347b51abb0b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15288,7 +15291,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e0173ed5-c078-42e0-a379-cf382d2e5257}">
+          <x14:cfRule type="dataBar" id="{e84d9e76-e88d-4c96-8d71-8b07e6351517}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15297,7 +15300,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{65cc7cf5-14c0-4b5f-811f-ca1b8efbbbd6}">
+          <x14:cfRule type="dataBar" id="{359dbfec-4a6c-40e0-ae76-2bb1f799150b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15309,7 +15312,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d4b99512-e121-4139-bf4f-478598f3b8ed}">
+          <x14:cfRule type="dataBar" id="{949907f8-4e5c-4f63-b0b4-7f0ee70501df}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15320,7 +15323,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b7990eb3-e2a8-4729-9627-76a9d283c86b}">
+          <x14:cfRule type="dataBar" id="{6f92c482-7162-48e9-9c4d-24b6585ae2ea}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15331,14 +15334,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{75d7fee4-819b-44d9-8b20-6a7c4d59367a}">
+          <x14:cfRule type="dataBar" id="{77a4be30-fb90-4bb1-9e17-6ff215ab8dd2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bf167ec8-97f8-4a4f-ba88-8c79cb10fc18}">
+          <x14:cfRule type="dataBar" id="{2ae61df5-24dc-4007-8682-ca1b39fc4457}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15349,7 +15352,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{39c6f328-e21c-487e-9581-bddc8a5f186d}">
+          <x14:cfRule type="dataBar" id="{e218c815-f620-4ab9-b2c1-c619e5672944}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15360,7 +15363,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c3c70eec-574d-4356-a558-48c9608afde4}">
+          <x14:cfRule type="dataBar" id="{48bb6745-e35a-4ac4-8113-3e4b2199b3e7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15371,7 +15374,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{021101b6-8b46-487c-b045-56b47db6efe3}">
+          <x14:cfRule type="dataBar" id="{59f633d6-7aee-47fb-a523-11c281ebe6f4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15380,7 +15383,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{454fa8b0-dc96-45a7-9abf-4fe778497fd0}">
+          <x14:cfRule type="dataBar" id="{49f06d25-c74f-43ff-9142-1acd8553f4e1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15392,7 +15395,7 @@
           <xm:sqref>K57:K58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{660c922d-c322-4e1f-8fb1-db4774b5108c}">
+          <x14:cfRule type="dataBar" id="{45f5d649-00d2-4773-a3e7-bc4d5f60ef11}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15404,7 +15407,7 @@
           <xm:sqref>K187:K206</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ae039ae-cfd2-4723-806c-aa9965162f54}">
+          <x14:cfRule type="dataBar" id="{0dede596-0dc9-4b96-a014-2eefbd147335}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15416,7 +15419,7 @@
           <xm:sqref>AD56:AE57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2669753b-ea0b-452e-8989-626ec7c7b8bd}">
+          <x14:cfRule type="dataBar" id="{f0516f3b-8c3c-44c2-b167-5a93f6df5fd0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15428,7 +15431,7 @@
           <xm:sqref>AD60:AE63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e19dd18-97db-4fd5-8e86-0653719ff076}">
+          <x14:cfRule type="dataBar" id="{64368faf-b4e7-461e-af1c-dfeeaf325e31}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15439,7 +15442,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9b018b58-33a7-48ff-9aec-861c382930c1}">
+          <x14:cfRule type="dataBar" id="{1de019e6-1729-48d5-9d12-b75b1dd4f460}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15450,14 +15453,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e3294e00-1e6c-4312-824c-622cd3063868}">
+          <x14:cfRule type="dataBar" id="{b504a1b0-d920-4a9f-abb6-7a720dd12403}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4dedcafa-b9ff-4bf4-b4eb-8fa8b925331c}">
+          <x14:cfRule type="dataBar" id="{cb764419-424c-4940-b947-4ec850a2b856}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15468,7 +15471,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d117c7c5-2c2b-4130-b77b-b6d2b8bd77a4}">
+          <x14:cfRule type="dataBar" id="{1c062047-08b2-41e7-868a-6b474c0ee37d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15479,7 +15482,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{eaecd9f0-0e92-426c-82df-369973eb2a9e}">
+          <x14:cfRule type="dataBar" id="{a3d88865-884d-47ad-b66b-474372e20f86}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15490,7 +15493,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d842f337-be2b-4ddd-aec6-41cd66fa1536}">
+          <x14:cfRule type="dataBar" id="{4884e0e4-e743-4ffc-bde7-844d246bc152}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15499,7 +15502,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b6816a42-ff2a-4f11-beb0-6f2a8e77605d}">
+          <x14:cfRule type="dataBar" id="{2e1b558b-473a-4472-8f54-ca32e7bb6c5c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15511,7 +15514,7 @@
           <xm:sqref>F67 F77 F87 F97 F107 F117 F127 F137 F147 F157 F167 F177</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{44ab21ed-40fd-4816-b690-93c0ce8ede0a}">
+          <x14:cfRule type="dataBar" id="{dd8e2e00-de06-45e3-9b2b-a57aea4e269b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15520,7 +15523,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6f762d2f-bcfb-44e4-9975-728c71e7802a}">
+          <x14:cfRule type="dataBar" id="{c7e8d78f-65c5-454d-9eaf-03c1a14b3eef}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15532,7 +15535,7 @@
           <xm:sqref>K67:K77 K83:K97 K103:K117 K123:K137 K143:K157 K163:K177 K183:K186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af3dccdd-07f0-40c8-83ea-21a3fee232b0}">
+          <x14:cfRule type="dataBar" id="{0ae70342-011e-4ad3-b967-dc71d675d58e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15544,7 +15547,7 @@
           <xm:sqref>Y67:Y77 Y83:Y97 Y103:Y120 Y123:Y139 Y143:Y158 Y163:Y177 Y183:Y186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7b110bb-9790-4d0d-8139-140a818cffdb}">
+          <x14:cfRule type="dataBar" id="{d211ee09-d714-45db-af85-1433cf06cd07}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15553,7 +15556,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5ba520d9-c72b-4e5f-86e8-bba8b29380f5}">
+          <x14:cfRule type="dataBar" id="{8485f837-5657-4eda-981f-97407c1c2f57}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15565,14 +15568,14 @@
           <xm:sqref>AB67 AB87 AB107 AB127 AB147 AB167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{da491c53-d03c-4bf2-b9ef-9823ffd28842}">
+          <x14:cfRule type="dataBar" id="{2f9c079a-1998-49b6-afe6-044c4ccc6f9f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{13738b4b-240a-488f-b083-178f2b5e040c}">
+          <x14:cfRule type="dataBar" id="{7d0009a4-dc70-4ead-885b-d95e41d1d924}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15584,7 +15587,7 @@
           <xm:sqref>AB67:AB77 AB83:AB97 AB103:AB120 AB123:AB139 AB143:AB158 AB163:AB177 AB183:AB186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba0c5448-d32a-4675-9089-76b81e755493}">
+          <x14:cfRule type="dataBar" id="{48bc4bd8-674b-40cb-b6d8-52024244c8bc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15596,7 +15599,7 @@
           <xm:sqref>AB67:AB77 AB83:AB97 AB103:AB117 AB123:AB137 AB143:AB157 AB163:AB177 AB183:AB186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8f451540-f630-4265-bc19-82120acc6706}">
+          <x14:cfRule type="dataBar" id="{60051a04-10f0-442d-999a-e9ae5310da52}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15605,7 +15608,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{17181710-2ecf-4e19-93a6-ef82998c0bfa}">
+          <x14:cfRule type="dataBar" id="{7144b85d-6e20-45dc-a107-a255a0033856}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15617,7 +15620,7 @@
           <xm:sqref>K78:K82 K98:K102 K118:K122 K138:K142 K158:K162 K178:K182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fd8c2d4f-9ca3-4f1a-b1b0-d72889cc5208}">
+          <x14:cfRule type="dataBar" id="{1208efef-11e3-4705-b89e-b066356f6415}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15629,14 +15632,14 @@
           <xm:sqref>Y78:Y82 Y98:Y102 Y118:Y122 Y138:Y142 Y158:Y162 Y178:Y182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{76a5327a-5948-46e7-9077-382bdfd2f832}">
+          <x14:cfRule type="dataBar" id="{9c26a5c8-58da-4fa6-9cad-f76bb37201a7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{47b64aed-da21-47f3-9440-c77a8fc347b9}">
+          <x14:cfRule type="dataBar" id="{01c24f63-9d3c-4c0d-bee5-4ddb336a725b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15645,7 +15648,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{581c8166-3232-4450-85b6-505e48de7565}">
+          <x14:cfRule type="dataBar" id="{dcb0dba8-1b04-4f3e-9b75-5d668b30cde2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15657,7 +15660,7 @@
           <xm:sqref>AB78:AB82 AB98:AB102 AB118:AB122 AB138:AB142 AB158:AB162 AB178:AB182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{407d13e1-aff9-41d1-8dc7-a8428c93ebec}">
+          <x14:cfRule type="dataBar" id="{1d130f01-ad99-4a14-a80c-c5945538fe3a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15666,7 +15669,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1d7204ba-4c9e-42e0-b4cc-31eadfa107ab}">
+          <x14:cfRule type="dataBar" id="{cdcfa7eb-837d-4eda-8489-80e85184b478}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15675,7 +15678,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fc2afdd3-dc76-469e-9597-311e18cdc97b}">
+          <x14:cfRule type="dataBar" id="{cd0b5d2e-333e-492d-b723-3a8de40cd710}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15687,7 +15690,7 @@
           <xm:sqref>F187 F192 F197 F202</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9fcb19b0-7885-49b2-b8e5-84a1f0c644d0}">
+          <x14:cfRule type="dataBar" id="{bb528e2a-aadb-4970-9798-264f351520d8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15696,7 +15699,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{62bf14c4-f22e-4706-aca6-3c89b91e71e1}">
+          <x14:cfRule type="dataBar" id="{c7ea6d54-2346-4a52-9b46-ee3ddc87ccfd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">

--- a/E楼交接班容量报表空模板.xlsx
+++ b/E楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="22020"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -3558,27 +3558,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE209"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="11.7685185185185" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7727272727273" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="17.1111111111111" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1090909090909" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
     <col min="20" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12.3363636363636" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4053,7 +4053,10 @@
       <c r="I12" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="50"/>
+      <c r="J12" s="50">
+        <f t="shared" ref="J12:J15" si="0">G12/10000</f>
+        <v>0</v>
+      </c>
       <c r="K12" s="13"/>
       <c r="L12" s="14"/>
       <c r="M12" s="51">
@@ -4096,7 +4099,10 @@
       <c r="I13" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="50"/>
+      <c r="J13" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K13" s="13"/>
       <c r="L13" s="14"/>
       <c r="M13" s="51">
@@ -4136,7 +4142,10 @@
       <c r="I14" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="50"/>
+      <c r="J14" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K14" s="13"/>
       <c r="L14" s="14"/>
       <c r="M14" s="51">
@@ -4177,7 +4186,10 @@
       <c r="I15" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="J15" s="50"/>
+      <c r="J15" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="K15" s="13"/>
       <c r="L15" s="14"/>
       <c r="M15" s="51">
@@ -5365,6 +5377,7 @@
         <v>89</v>
       </c>
       <c r="N38" s="102" t="e">
+        <f>N35-N36</f>
         <v>#VALUE!</v>
       </c>
       <c r="O38" s="52"/>
@@ -5400,6 +5413,7 @@
         <v>89</v>
       </c>
       <c r="AA38" s="101" t="e">
+        <f>AA35-AA36</f>
         <v>#VALUE!</v>
       </c>
       <c r="AB38" s="84" t="s">
@@ -5519,6 +5533,7 @@
         <v>100</v>
       </c>
       <c r="L40" s="101" t="e">
+        <f>L39-L35</f>
         <v>#VALUE!</v>
       </c>
       <c r="M40" s="99" t="s">
@@ -5552,6 +5567,7 @@
         <v>100</v>
       </c>
       <c r="Y40" s="101" t="e">
+        <f>Y39-Y35</f>
         <v>#VALUE!</v>
       </c>
       <c r="Z40" s="99" t="s">
@@ -5594,6 +5610,7 @@
         <v>105</v>
       </c>
       <c r="N41" s="102" t="e">
+        <f>N39-N40</f>
         <v>#VALUE!</v>
       </c>
       <c r="O41" s="52"/>
@@ -5619,6 +5636,7 @@
         <v>105</v>
       </c>
       <c r="AA41" s="101" t="e">
+        <f>AA39-AA40</f>
         <v>#VALUE!</v>
       </c>
       <c r="AB41" s="76"/>
@@ -6838,11 +6856,11 @@
       </c>
       <c r="T68" s="147"/>
       <c r="U68" s="148">
-        <f t="shared" ref="U68:U99" si="0">R68*0.935</f>
+        <f t="shared" ref="U68:U99" si="1">R68*0.935</f>
         <v>0</v>
       </c>
       <c r="V68" s="149">
-        <f t="shared" ref="V68:V99" si="1">U68/215</f>
+        <f t="shared" ref="V68:V99" si="2">U68/215</f>
         <v>0</v>
       </c>
       <c r="W68" s="155"/>
@@ -6881,11 +6899,11 @@
       </c>
       <c r="T69" s="147"/>
       <c r="U69" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V69" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W69" s="155"/>
@@ -6924,11 +6942,11 @@
       </c>
       <c r="T70" s="147"/>
       <c r="U70" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V70" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W70" s="155"/>
@@ -6967,11 +6985,11 @@
       </c>
       <c r="T71" s="147"/>
       <c r="U71" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V71" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W71" s="155"/>
@@ -7010,11 +7028,11 @@
       </c>
       <c r="T72" s="147"/>
       <c r="U72" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V72" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W72" s="155"/>
@@ -7053,11 +7071,11 @@
       </c>
       <c r="T73" s="147"/>
       <c r="U73" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V73" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W73" s="155"/>
@@ -7096,11 +7114,11 @@
       </c>
       <c r="T74" s="147"/>
       <c r="U74" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V74" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W74" s="155"/>
@@ -7139,11 +7157,11 @@
       </c>
       <c r="T75" s="147"/>
       <c r="U75" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V75" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W75" s="155"/>
@@ -7182,11 +7200,11 @@
       </c>
       <c r="T76" s="147"/>
       <c r="U76" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V76" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W76" s="155"/>
@@ -7234,11 +7252,11 @@
       </c>
       <c r="T77" s="147"/>
       <c r="U77" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V77" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W77" s="155"/>
@@ -7279,11 +7297,11 @@
       </c>
       <c r="T78" s="147"/>
       <c r="U78" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V78" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W78" s="155"/>
@@ -7322,11 +7340,11 @@
       </c>
       <c r="T79" s="147"/>
       <c r="U79" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V79" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W79" s="155"/>
@@ -7365,11 +7383,11 @@
       </c>
       <c r="T80" s="147"/>
       <c r="U80" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V80" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W80" s="155"/>
@@ -7408,11 +7426,11 @@
       </c>
       <c r="T81" s="147"/>
       <c r="U81" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V81" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W81" s="155"/>
@@ -7451,11 +7469,11 @@
       </c>
       <c r="T82" s="147"/>
       <c r="U82" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V82" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W82" s="155"/>
@@ -7494,11 +7512,11 @@
       </c>
       <c r="T83" s="147"/>
       <c r="U83" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V83" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W83" s="155"/>
@@ -7537,11 +7555,11 @@
       </c>
       <c r="T84" s="147"/>
       <c r="U84" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V84" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W84" s="155"/>
@@ -7580,11 +7598,11 @@
       </c>
       <c r="T85" s="147"/>
       <c r="U85" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V85" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W85" s="155"/>
@@ -7623,11 +7641,11 @@
       </c>
       <c r="T86" s="147"/>
       <c r="U86" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V86" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W86" s="155"/>
@@ -7684,11 +7702,11 @@
       </c>
       <c r="T87" s="147"/>
       <c r="U87" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V87" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W87" s="140">
@@ -7748,11 +7766,11 @@
       </c>
       <c r="T88" s="147"/>
       <c r="U88" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V88" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W88" s="155"/>
@@ -7791,11 +7809,11 @@
       </c>
       <c r="T89" s="147"/>
       <c r="U89" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V89" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W89" s="155"/>
@@ -7834,11 +7852,11 @@
       </c>
       <c r="T90" s="147"/>
       <c r="U90" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V90" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W90" s="155"/>
@@ -7877,11 +7895,11 @@
       </c>
       <c r="T91" s="147"/>
       <c r="U91" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V91" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W91" s="155"/>
@@ -7920,11 +7938,11 @@
       </c>
       <c r="T92" s="147"/>
       <c r="U92" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V92" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W92" s="155"/>
@@ -7963,11 +7981,11 @@
       </c>
       <c r="T93" s="147"/>
       <c r="U93" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V93" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W93" s="155"/>
@@ -8006,11 +8024,11 @@
       </c>
       <c r="T94" s="147"/>
       <c r="U94" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V94" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W94" s="155"/>
@@ -8049,11 +8067,11 @@
       </c>
       <c r="T95" s="147"/>
       <c r="U95" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V95" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W95" s="155"/>
@@ -8092,11 +8110,11 @@
       </c>
       <c r="T96" s="147"/>
       <c r="U96" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V96" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W96" s="155"/>
@@ -8144,11 +8162,11 @@
       </c>
       <c r="T97" s="147"/>
       <c r="U97" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V97" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W97" s="155"/>
@@ -8189,11 +8207,11 @@
       </c>
       <c r="T98" s="147"/>
       <c r="U98" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V98" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W98" s="155"/>
@@ -8232,11 +8250,11 @@
       </c>
       <c r="T99" s="147"/>
       <c r="U99" s="148">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V99" s="149">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W99" s="155"/>
@@ -8275,11 +8293,11 @@
       </c>
       <c r="T100" s="147"/>
       <c r="U100" s="148">
-        <f t="shared" ref="U100:U131" si="2">R100*0.935</f>
+        <f t="shared" ref="U100:U131" si="3">R100*0.935</f>
         <v>0</v>
       </c>
       <c r="V100" s="149">
-        <f t="shared" ref="V100:V131" si="3">U100/215</f>
+        <f t="shared" ref="V100:V131" si="4">U100/215</f>
         <v>0</v>
       </c>
       <c r="W100" s="155"/>
@@ -8318,11 +8336,11 @@
       </c>
       <c r="T101" s="147"/>
       <c r="U101" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V101" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W101" s="155"/>
@@ -8361,11 +8379,11 @@
       </c>
       <c r="T102" s="147"/>
       <c r="U102" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V102" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W102" s="155"/>
@@ -8404,11 +8422,11 @@
       </c>
       <c r="T103" s="147"/>
       <c r="U103" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V103" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W103" s="155"/>
@@ -8447,11 +8465,11 @@
       </c>
       <c r="T104" s="147"/>
       <c r="U104" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V104" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W104" s="155"/>
@@ -8490,11 +8508,11 @@
       </c>
       <c r="T105" s="147"/>
       <c r="U105" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V105" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W105" s="155"/>
@@ -8533,11 +8551,11 @@
       </c>
       <c r="T106" s="147"/>
       <c r="U106" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V106" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W106" s="155"/>
@@ -8594,11 +8612,11 @@
       </c>
       <c r="T107" s="147"/>
       <c r="U107" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V107" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W107" s="140">
@@ -8658,11 +8676,11 @@
       </c>
       <c r="T108" s="147"/>
       <c r="U108" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V108" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W108" s="155"/>
@@ -8701,11 +8719,11 @@
       </c>
       <c r="T109" s="147"/>
       <c r="U109" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V109" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W109" s="155"/>
@@ -8744,11 +8762,11 @@
       </c>
       <c r="T110" s="147"/>
       <c r="U110" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V110" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W110" s="155"/>
@@ -8787,11 +8805,11 @@
       </c>
       <c r="T111" s="147"/>
       <c r="U111" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V111" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W111" s="155"/>
@@ -8830,11 +8848,11 @@
       </c>
       <c r="T112" s="147"/>
       <c r="U112" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V112" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W112" s="155"/>
@@ -8873,11 +8891,11 @@
       </c>
       <c r="T113" s="147"/>
       <c r="U113" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V113" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W113" s="155"/>
@@ -8916,11 +8934,11 @@
       </c>
       <c r="T114" s="147"/>
       <c r="U114" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V114" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W114" s="155"/>
@@ -8959,11 +8977,11 @@
       </c>
       <c r="T115" s="147"/>
       <c r="U115" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V115" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W115" s="155"/>
@@ -9002,11 +9020,11 @@
       </c>
       <c r="T116" s="147"/>
       <c r="U116" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V116" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W116" s="155"/>
@@ -9054,11 +9072,11 @@
       </c>
       <c r="T117" s="147"/>
       <c r="U117" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V117" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W117" s="155"/>
@@ -9099,11 +9117,11 @@
       </c>
       <c r="T118" s="147"/>
       <c r="U118" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V118" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W118" s="155"/>
@@ -9142,11 +9160,11 @@
       </c>
       <c r="T119" s="147"/>
       <c r="U119" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V119" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W119" s="155"/>
@@ -9185,11 +9203,11 @@
       </c>
       <c r="T120" s="147"/>
       <c r="U120" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V120" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W120" s="155"/>
@@ -9228,11 +9246,11 @@
       </c>
       <c r="T121" s="147"/>
       <c r="U121" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V121" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W121" s="155"/>
@@ -9271,11 +9289,11 @@
       </c>
       <c r="T122" s="147"/>
       <c r="U122" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V122" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W122" s="155"/>
@@ -9314,11 +9332,11 @@
       </c>
       <c r="T123" s="147"/>
       <c r="U123" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V123" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W123" s="155"/>
@@ -9357,11 +9375,11 @@
       </c>
       <c r="T124" s="147"/>
       <c r="U124" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V124" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W124" s="155"/>
@@ -9400,11 +9418,11 @@
       </c>
       <c r="T125" s="147"/>
       <c r="U125" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V125" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W125" s="155"/>
@@ -9443,11 +9461,11 @@
       </c>
       <c r="T126" s="147"/>
       <c r="U126" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V126" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W126" s="155"/>
@@ -9504,11 +9522,11 @@
       </c>
       <c r="T127" s="147"/>
       <c r="U127" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V127" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W127" s="140">
@@ -9568,11 +9586,11 @@
       </c>
       <c r="T128" s="147"/>
       <c r="U128" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V128" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W128" s="155"/>
@@ -9611,11 +9629,11 @@
       </c>
       <c r="T129" s="147"/>
       <c r="U129" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V129" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W129" s="155"/>
@@ -9654,11 +9672,11 @@
       </c>
       <c r="T130" s="147"/>
       <c r="U130" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V130" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W130" s="155"/>
@@ -9697,11 +9715,11 @@
       </c>
       <c r="T131" s="147"/>
       <c r="U131" s="148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V131" s="149">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W131" s="155"/>
@@ -9740,11 +9758,11 @@
       </c>
       <c r="T132" s="147"/>
       <c r="U132" s="148">
-        <f t="shared" ref="U132:U163" si="4">R132*0.935</f>
+        <f t="shared" ref="U132:U163" si="5">R132*0.935</f>
         <v>0</v>
       </c>
       <c r="V132" s="149">
-        <f t="shared" ref="V132:V163" si="5">U132/215</f>
+        <f t="shared" ref="V132:V163" si="6">U132/215</f>
         <v>0</v>
       </c>
       <c r="W132" s="155"/>
@@ -9783,11 +9801,11 @@
       </c>
       <c r="T133" s="147"/>
       <c r="U133" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V133" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W133" s="155"/>
@@ -9826,11 +9844,11 @@
       </c>
       <c r="T134" s="147"/>
       <c r="U134" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V134" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W134" s="155"/>
@@ -9869,11 +9887,11 @@
       </c>
       <c r="T135" s="147"/>
       <c r="U135" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V135" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W135" s="155"/>
@@ -9912,11 +9930,11 @@
       </c>
       <c r="T136" s="147"/>
       <c r="U136" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V136" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W136" s="155"/>
@@ -9964,11 +9982,11 @@
       </c>
       <c r="T137" s="147"/>
       <c r="U137" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V137" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W137" s="155"/>
@@ -10009,11 +10027,11 @@
       </c>
       <c r="T138" s="147"/>
       <c r="U138" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V138" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W138" s="155"/>
@@ -10052,11 +10070,11 @@
       </c>
       <c r="T139" s="147"/>
       <c r="U139" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V139" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W139" s="155"/>
@@ -10095,11 +10113,11 @@
       </c>
       <c r="T140" s="147"/>
       <c r="U140" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V140" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W140" s="155"/>
@@ -10138,11 +10156,11 @@
       </c>
       <c r="T141" s="147"/>
       <c r="U141" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V141" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W141" s="155"/>
@@ -10181,11 +10199,11 @@
       </c>
       <c r="T142" s="147"/>
       <c r="U142" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V142" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W142" s="155"/>
@@ -10224,11 +10242,11 @@
       </c>
       <c r="T143" s="147"/>
       <c r="U143" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V143" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W143" s="155"/>
@@ -10267,11 +10285,11 @@
       </c>
       <c r="T144" s="147"/>
       <c r="U144" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V144" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W144" s="155"/>
@@ -10310,11 +10328,11 @@
       </c>
       <c r="T145" s="147"/>
       <c r="U145" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V145" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W145" s="155"/>
@@ -10353,11 +10371,11 @@
       </c>
       <c r="T146" s="147"/>
       <c r="U146" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V146" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W146" s="155"/>
@@ -10414,11 +10432,11 @@
       </c>
       <c r="T147" s="147"/>
       <c r="U147" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V147" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W147" s="140">
@@ -10478,11 +10496,11 @@
       </c>
       <c r="T148" s="147"/>
       <c r="U148" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V148" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W148" s="155"/>
@@ -10521,11 +10539,11 @@
       </c>
       <c r="T149" s="147"/>
       <c r="U149" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V149" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W149" s="155"/>
@@ -10564,11 +10582,11 @@
       </c>
       <c r="T150" s="147"/>
       <c r="U150" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V150" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W150" s="155"/>
@@ -10607,11 +10625,11 @@
       </c>
       <c r="T151" s="147"/>
       <c r="U151" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V151" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W151" s="155"/>
@@ -10650,11 +10668,11 @@
       </c>
       <c r="T152" s="147"/>
       <c r="U152" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V152" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W152" s="155"/>
@@ -10693,11 +10711,11 @@
       </c>
       <c r="T153" s="147"/>
       <c r="U153" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V153" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W153" s="155"/>
@@ -10736,11 +10754,11 @@
       </c>
       <c r="T154" s="147"/>
       <c r="U154" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V154" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W154" s="155"/>
@@ -10779,11 +10797,11 @@
       </c>
       <c r="T155" s="147"/>
       <c r="U155" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V155" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W155" s="155"/>
@@ -10822,11 +10840,11 @@
       </c>
       <c r="T156" s="147"/>
       <c r="U156" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V156" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W156" s="155"/>
@@ -10874,11 +10892,11 @@
       </c>
       <c r="T157" s="147"/>
       <c r="U157" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V157" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W157" s="155"/>
@@ -10919,11 +10937,11 @@
       </c>
       <c r="T158" s="147"/>
       <c r="U158" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V158" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W158" s="155"/>
@@ -10962,11 +10980,11 @@
       </c>
       <c r="T159" s="147"/>
       <c r="U159" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V159" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W159" s="155"/>
@@ -11005,11 +11023,11 @@
       </c>
       <c r="T160" s="147"/>
       <c r="U160" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V160" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W160" s="155"/>
@@ -11048,11 +11066,11 @@
       </c>
       <c r="T161" s="147"/>
       <c r="U161" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V161" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W161" s="155"/>
@@ -11091,11 +11109,11 @@
       </c>
       <c r="T162" s="147"/>
       <c r="U162" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V162" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W162" s="155"/>
@@ -11134,11 +11152,11 @@
       </c>
       <c r="T163" s="147"/>
       <c r="U163" s="148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V163" s="149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W163" s="155"/>
@@ -11177,11 +11195,11 @@
       </c>
       <c r="T164" s="147"/>
       <c r="U164" s="148">
-        <f t="shared" ref="U164:U186" si="6">R164*0.935</f>
+        <f t="shared" ref="U164:U186" si="7">R164*0.935</f>
         <v>0</v>
       </c>
       <c r="V164" s="149">
-        <f t="shared" ref="V164:V186" si="7">U164/215</f>
+        <f t="shared" ref="V164:V186" si="8">U164/215</f>
         <v>0</v>
       </c>
       <c r="W164" s="155"/>
@@ -11220,11 +11238,11 @@
       </c>
       <c r="T165" s="147"/>
       <c r="U165" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V165" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W165" s="155"/>
@@ -11263,11 +11281,11 @@
       </c>
       <c r="T166" s="168"/>
       <c r="U166" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V166" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W166" s="155"/>
@@ -11324,11 +11342,11 @@
       </c>
       <c r="T167" s="147"/>
       <c r="U167" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V167" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W167" s="117">
@@ -11388,11 +11406,11 @@
       </c>
       <c r="T168" s="147"/>
       <c r="U168" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V168" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W168" s="117"/>
@@ -11431,11 +11449,11 @@
       </c>
       <c r="T169" s="147"/>
       <c r="U169" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V169" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W169" s="117"/>
@@ -11474,11 +11492,11 @@
       </c>
       <c r="T170" s="147"/>
       <c r="U170" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V170" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W170" s="117"/>
@@ -11517,11 +11535,11 @@
       </c>
       <c r="T171" s="147"/>
       <c r="U171" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V171" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W171" s="117"/>
@@ -11560,11 +11578,11 @@
       </c>
       <c r="T172" s="147"/>
       <c r="U172" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V172" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W172" s="117"/>
@@ -11603,11 +11621,11 @@
       </c>
       <c r="T173" s="147"/>
       <c r="U173" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V173" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W173" s="117"/>
@@ -11646,11 +11664,11 @@
       </c>
       <c r="T174" s="147"/>
       <c r="U174" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V174" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W174" s="117"/>
@@ -11689,11 +11707,11 @@
       </c>
       <c r="T175" s="147"/>
       <c r="U175" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V175" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W175" s="117"/>
@@ -11732,11 +11750,11 @@
       </c>
       <c r="T176" s="147"/>
       <c r="U176" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V176" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W176" s="117"/>
@@ -11784,11 +11802,11 @@
       </c>
       <c r="T177" s="147"/>
       <c r="U177" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V177" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W177" s="117"/>
@@ -11829,11 +11847,11 @@
       </c>
       <c r="T178" s="147"/>
       <c r="U178" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V178" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W178" s="117"/>
@@ -11872,11 +11890,11 @@
       </c>
       <c r="T179" s="147"/>
       <c r="U179" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V179" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W179" s="117"/>
@@ -11915,11 +11933,11 @@
       </c>
       <c r="T180" s="147"/>
       <c r="U180" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V180" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W180" s="117"/>
@@ -11958,11 +11976,11 @@
       </c>
       <c r="T181" s="147"/>
       <c r="U181" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V181" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W181" s="117"/>
@@ -12001,11 +12019,11 @@
       </c>
       <c r="T182" s="147"/>
       <c r="U182" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V182" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W182" s="117"/>
@@ -12044,11 +12062,11 @@
       </c>
       <c r="T183" s="147"/>
       <c r="U183" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V183" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W183" s="117"/>
@@ -12087,11 +12105,11 @@
       </c>
       <c r="T184" s="147"/>
       <c r="U184" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V184" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W184" s="117"/>
@@ -12130,11 +12148,11 @@
       </c>
       <c r="T185" s="147"/>
       <c r="U185" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V185" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W185" s="117"/>
@@ -12173,11 +12191,11 @@
       </c>
       <c r="T186" s="147"/>
       <c r="U186" s="148">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V186" s="149">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W186" s="117"/>
@@ -13729,7 +13747,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a7cf097-df01-4e0b-9c15-a9520084a047}</x14:id>
+          <x14:id>{f8dd37d9-0ad5-43ba-9e35-7d0bb24ed270}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13741,7 +13759,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e089d27f-319d-4e28-bd37-efc0b033cfc7}</x14:id>
+          <x14:id>{b0d436f5-3229-4e8e-a7be-071cc8361450}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13753,7 +13771,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d35d9069-c9a0-4da7-a7c4-419ec500b026}</x14:id>
+          <x14:id>{be026398-f23f-47f9-a85d-b340982e0178}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13765,7 +13783,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c2d94e93-1b56-4eb4-9e6f-c33c853e1c77}</x14:id>
+          <x14:id>{029df8e6-0956-4a91-916d-122e5f33b9c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13777,7 +13795,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{76cdfebc-9db3-482f-bfc3-def288690108}</x14:id>
+          <x14:id>{c8701642-e5a1-406e-ab30-8e7cc02d3054}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13789,7 +13807,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{68b3368b-e8b4-4e26-b354-fd18a580f61e}</x14:id>
+          <x14:id>{26e4c31b-1c51-4349-a562-5d18703bba34}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13801,7 +13819,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b4982086-d8eb-4fc1-997a-d71e5117e6b8}</x14:id>
+          <x14:id>{2c636625-5ee4-48b6-b562-4f7ef85fbce9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13813,7 +13831,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f0a9c45-c056-4908-adca-b14c586308de}</x14:id>
+          <x14:id>{7a2d6eea-828a-4650-b51d-2f302d9b1a82}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13827,7 +13845,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{50fae88e-4780-4f8d-aa46-e4722fe2eb44}</x14:id>
+          <x14:id>{1a52e1de-6eb6-4d70-a9d8-60445feed595}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13839,7 +13857,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23f4d11f-2cbc-4ad5-b62b-395942c8602f}</x14:id>
+          <x14:id>{cdd8209b-80ca-4136-a546-4feee398ccf6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13851,7 +13869,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{109d98cd-c981-40c8-b949-0e9f27db7853}</x14:id>
+          <x14:id>{7c9d5dfe-46d7-44a6-b475-56c7fe0ec83b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13863,7 +13881,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{049ea757-1ce1-448c-8e67-8fadea3280a7}</x14:id>
+          <x14:id>{d0aa2ba4-66a0-48ae-b2fd-816b297697ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13875,7 +13893,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{086827ad-e785-429a-9c71-16a0e77b4030}</x14:id>
+          <x14:id>{5fb1dfb4-d6a7-4d46-bcc8-66d8c0fa52db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13887,7 +13905,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f672a979-3f33-4a69-8839-803b11288e7f}</x14:id>
+          <x14:id>{2f3ab93f-1540-436e-a3b5-73313e4187ab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13899,7 +13917,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db06766a-dd6f-4188-98b5-f34a9965f435}</x14:id>
+          <x14:id>{0b904468-8224-4e3e-8598-90264cecb5ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13911,7 +13929,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{696e0f09-e970-444c-8e9d-5ff06a6fc217}</x14:id>
+          <x14:id>{3e298ad2-4e9e-4051-b80d-b7396a240037}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13925,7 +13943,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{95624c8a-c21e-49e8-b505-e960145bfe20}</x14:id>
+          <x14:id>{9aa3e44d-8053-4c56-868c-7f597fb234af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13937,7 +13955,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a8cff09-fb14-41ae-9be6-6dcad1c2d62a}</x14:id>
+          <x14:id>{82900eb9-f94f-4a18-b6c2-8bcbc616ae4a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13949,7 +13967,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a662f02d-9568-4431-8220-0777cfe8e2a5}</x14:id>
+          <x14:id>{9bf4d7b7-3db2-4cd9-be29-3d856e10f757}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13961,7 +13979,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d399629e-d9bb-4acf-9b9d-9ba683bd366a}</x14:id>
+          <x14:id>{7420a9d9-0f7c-44c3-8a61-0e3e5577ad3e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13973,7 +13991,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0b322cfc-731c-4df8-bc06-58164d180acb}</x14:id>
+          <x14:id>{303ca555-4201-42ed-9633-c7949e4d9294}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13985,7 +14003,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bda07511-7290-4553-bfe2-35056849b2df}</x14:id>
+          <x14:id>{eae7986d-503c-44a8-9171-bc3561b17299}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13997,7 +14015,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b93ffeee-5bf1-421c-838c-bf4de6cece05}</x14:id>
+          <x14:id>{42c6def2-d975-4e92-87ce-58609debe97c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14009,7 +14027,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{35daef96-d3ff-4bc3-bdfc-cd37db7f90a7}</x14:id>
+          <x14:id>{20287a30-46b1-40f1-9081-a6c2a093b1a8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14023,7 +14041,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{598d98f2-f70a-48fb-abd2-168da8c2c372}</x14:id>
+          <x14:id>{3202fa0b-f4ed-4171-b289-aec41fe50532}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14035,7 +14053,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1d8dafe6-f99a-47d5-8594-dab72d7ae623}</x14:id>
+          <x14:id>{745b3fb3-b2da-495d-8f07-be9b757cf5fd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14047,7 +14065,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{77e2fc71-0f21-44a1-8646-9d8eee8c22fb}</x14:id>
+          <x14:id>{5e30146e-5cd1-493f-b54e-4e08fbae3eea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14059,7 +14077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5e09c52-cd31-4b6e-b1ac-7bb599551704}</x14:id>
+          <x14:id>{aed28516-5b29-4e25-9c92-b3f9b3bc1f6b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14071,7 +14089,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e31f85c0-71c9-40c7-a0b6-cffbeca2087f}</x14:id>
+          <x14:id>{26e679be-149b-402d-934e-64533685dfe4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14083,7 +14101,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4de0de1-6127-443f-91c1-4a963c37e8ef}</x14:id>
+          <x14:id>{ee212af3-5807-4713-9975-eb8868d806a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14095,7 +14113,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{563c6788-ec54-4d80-89b9-db9b5080014c}</x14:id>
+          <x14:id>{35e391e1-ccb4-4956-9cfc-d631ef73bd00}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14107,7 +14125,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{595bc562-8d3e-492a-bd31-48e904e64f13}</x14:id>
+          <x14:id>{6913ae6d-44f5-4cc4-842d-9c19918c096f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14121,7 +14139,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{08ffc4e0-988f-4545-8298-e9161412790a}</x14:id>
+          <x14:id>{1d0afa0a-fca3-4488-a9d4-785e71508049}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14133,7 +14151,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00563520-ba08-4058-abde-fbb4d465471d}</x14:id>
+          <x14:id>{f75b6ff3-9860-47e5-9d28-080d2b90a20a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14145,7 +14163,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e5e8c13f-273f-4eb2-bc9f-8a941e4e050b}</x14:id>
+          <x14:id>{2ef951a1-581d-459a-b5fc-c25d83f517de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14157,7 +14175,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7d00a515-cb09-40a2-a159-1162f189d47c}</x14:id>
+          <x14:id>{e2c4edd3-dcf1-4010-9994-04ae989354c0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14169,7 +14187,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24bf41a5-5384-4153-afe5-826e83b25494}</x14:id>
+          <x14:id>{06794649-bf22-42bd-922a-f8a03aefec74}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14181,7 +14199,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57c411a5-ff59-4789-8ef7-addc0a6ffcea}</x14:id>
+          <x14:id>{ba91d3f2-b574-41df-98db-389b1a4aa89e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14193,7 +14211,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{598c5f0c-a92d-4b1a-ba2c-4176a167d1f9}</x14:id>
+          <x14:id>{7acf6793-72e5-4515-9d50-406fab175039}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14205,7 +14223,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{941d4a85-4a07-43fa-b94c-2e1c676a6a29}</x14:id>
+          <x14:id>{4bd42acc-397b-4f0e-9235-9dab75ccde1b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14219,7 +14237,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{605d2638-6f65-412a-b83b-548ea6e84f99}</x14:id>
+          <x14:id>{61983b95-1bc7-45bf-a7e1-0d77a4be1697}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14231,7 +14249,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8bc4db2c-9bce-4e01-945d-cff136543605}</x14:id>
+          <x14:id>{2256cc2f-038c-4121-8614-58c08f36139a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14243,7 +14261,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{78a77489-9ed9-4049-aa3a-9429d8eda6a5}</x14:id>
+          <x14:id>{0ccfacc4-2e98-4aeb-a8f9-d2e87436df17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14255,7 +14273,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38f40bb0-97af-4254-904b-0e84e90b512a}</x14:id>
+          <x14:id>{2e9f8857-0abc-4084-af13-fcec883be745}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14267,7 +14285,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91a93edd-0e7f-4bc0-9c07-a4ba8130d3d4}</x14:id>
+          <x14:id>{2d0bf7fc-46d4-4127-a1c2-289fae48076c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14279,7 +14297,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8de5a738-3150-4715-b673-92c4d3506eaa}</x14:id>
+          <x14:id>{561b35bf-f1ac-4a7d-bca2-203b680b519d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14291,7 +14309,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{02075783-6d6d-457d-bd78-cdebbee61576}</x14:id>
+          <x14:id>{900016d7-d64c-4f8e-bda0-7d9f370628b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14303,7 +14321,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{30e7bda7-859c-4976-ac8d-f987302bc234}</x14:id>
+          <x14:id>{b7c9ef0f-bf41-4dfb-b749-c2f229d5b122}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14317,7 +14335,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c060139e-4097-4a98-a8a5-979557268789}</x14:id>
+          <x14:id>{613aa387-d0b6-45cb-b3cd-1d9d32ddfd5d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14329,7 +14347,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d976fd5e-551f-4e6d-9144-cf5457170844}</x14:id>
+          <x14:id>{16c7c2d2-7e07-4860-aa0f-0efd88aa3683}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14341,7 +14359,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c99d7190-788d-4273-903f-0714294f3b8b}</x14:id>
+          <x14:id>{53d60f3b-8c98-4283-bb23-3603259cc149}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14353,7 +14371,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b457db95-d0de-4c28-8796-38334285842f}</x14:id>
+          <x14:id>{2f104416-c5d5-47bc-ad2f-bf622e99b789}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14365,7 +14383,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25bdc30b-d4c4-45cf-a2b1-befad951804d}</x14:id>
+          <x14:id>{2beb57a7-a286-4c26-bfeb-66e8108b93c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14377,7 +14395,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e68fd87a-916a-4d03-8fa7-9cf4cd9755e5}</x14:id>
+          <x14:id>{d54625bc-01b6-4e8f-862e-9be617c7b7ab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14389,7 +14407,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a7bd11d-aaff-4668-9029-0762701eca5b}</x14:id>
+          <x14:id>{f89376e1-71a2-45df-b009-60b6b96f1f50}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14401,7 +14419,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b3f4be2-0197-466a-ab01-c04b8792ec8b}</x14:id>
+          <x14:id>{e1c1f213-9562-492f-849e-236a6fbd0afe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14415,7 +14433,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a9a8bf0-2cb3-4057-af38-bebd480260ae}</x14:id>
+          <x14:id>{bd660bf2-c44c-4355-8b61-67fd74d67f4d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14429,7 +14447,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a8dce3a7-ee08-4a34-9ac1-8f9e673ba224}</x14:id>
+          <x14:id>{d7b01846-ff5f-481e-94e6-fb0a080b2058}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14443,7 +14461,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9780f81e-354d-44eb-9157-f708e85c65e0}</x14:id>
+          <x14:id>{00eb0ea0-78b5-4e5d-b53c-76495df8839b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14457,7 +14475,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3f60dffe-320c-457c-b5e1-222aae6f870b}</x14:id>
+          <x14:id>{6550637d-847b-4599-9131-1762b5cb3de1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14469,7 +14487,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5323ee68-9b71-4f5a-9843-9ff32b9eb99c}</x14:id>
+          <x14:id>{8427225c-5b24-4584-bfd1-e11d4fccbedd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14481,7 +14499,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c1144dc-f6b5-4acb-8e24-d67cd9b6a9e4}</x14:id>
+          <x14:id>{9654132b-b282-4a5b-a230-f7208da4e900}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14493,7 +14511,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ceeb4f2f-567b-4d52-8441-1ec014249014}</x14:id>
+          <x14:id>{933bdeb4-44f9-44cf-ab09-b6005fc7e759}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14505,7 +14523,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0cebd8f3-72d0-4661-82fe-75a26b6013f9}</x14:id>
+          <x14:id>{3a53b751-6b45-49a0-9e96-936c8e27db7e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14517,7 +14535,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d2724b8-3cb2-48c5-9699-8bce34f2cedf}</x14:id>
+          <x14:id>{4106a878-16bf-48eb-8b3b-0972440acf08}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14529,7 +14547,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a168e323-b733-44e6-826c-bf7b0571002a}</x14:id>
+          <x14:id>{fb538c8a-81d7-4e6a-b8ad-bc38c7f210b0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14541,7 +14559,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0542ffd4-fc81-4605-99f1-6944753e696a}</x14:id>
+          <x14:id>{2d8862f3-0d74-4922-bb60-d1d261292f08}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14555,7 +14573,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab77f350-c989-419e-970a-228d838e70a5}</x14:id>
+          <x14:id>{1c19f651-ee91-4534-98cb-c3b3b089846e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14567,7 +14585,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e37c347-0c52-4517-a794-b5b0da5b3255}</x14:id>
+          <x14:id>{4d636ca4-5be8-423d-b0b9-435b8e2c8b3a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14581,7 +14599,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ce86388-d070-4721-9114-b6f67df5a7cc}</x14:id>
+          <x14:id>{1720642c-3530-4294-b7a2-ef11d2537329}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14595,7 +14613,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{932afb0c-44af-453d-b841-9bb36363ab9e}</x14:id>
+          <x14:id>{c64afc50-7e6a-4843-84c9-f4849e154217}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14607,7 +14625,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0bf539db-74d2-494e-9386-ccaa3e813c24}</x14:id>
+          <x14:id>{03801493-5bcb-47a5-bddc-85d8a7a74842}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14621,7 +14639,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a9621808-fad4-4e6d-a303-6495c0ac0736}</x14:id>
+          <x14:id>{6e051b41-a042-40ef-a400-0d4fddd228d2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14633,7 +14651,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38c3df44-ab19-4d88-9bf6-c328ea9f830b}</x14:id>
+          <x14:id>{e684fbb5-17d2-4457-a3ae-6558557579ab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14647,7 +14665,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b68a37ab-e99b-4017-ac20-089d85f9fe13}</x14:id>
+          <x14:id>{42403239-53de-48af-a42d-aa64ebacf436}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14661,7 +14679,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1fbd06b1-8b44-4327-8ab8-aee20e156610}</x14:id>
+          <x14:id>{742bfa9f-9d44-43dd-b116-ed385c276ca6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14673,7 +14691,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ca2b57c7-7278-4369-adb3-09056b9e097b}</x14:id>
+          <x14:id>{4996df7b-5f2d-4074-8b41-77825d0712d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14687,7 +14705,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8aea28ba-1af0-4071-8f76-2e6af242d094}</x14:id>
+          <x14:id>{d9a26976-b2ba-49d8-8b04-d1fcac6ff96b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14701,7 +14719,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38c53682-7597-4f43-8647-7d64657c6e15}</x14:id>
+          <x14:id>{48c576ba-f0fd-4b5c-b49d-b2c3f93b50e3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14713,7 +14731,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91b3922e-0b32-4e30-a97a-cf1bc03a31e0}</x14:id>
+          <x14:id>{6938760b-39c8-44e2-8b84-d6851891aaff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14725,7 +14743,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ed537be-4162-44d1-95bb-bd6cddf59bf9}</x14:id>
+          <x14:id>{cf8b3961-3bfa-4122-9fb2-16b5899749d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14739,7 +14757,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9f174a21-7a40-4d20-9a6e-2b2aa049a29f}</x14:id>
+          <x14:id>{8cfe7356-68c5-4e73-b277-efd491d8053d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14751,7 +14769,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6bf99c71-fda8-48e0-84a1-f8f9028430a1}</x14:id>
+          <x14:id>{89675322-6524-47bc-8883-30daea2addbe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14763,7 +14781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39476877-9ea9-4f8c-bb85-d64ed872b47e}</x14:id>
+          <x14:id>{62b2b25e-fc64-4ae1-ba88-6127f2947d66}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14777,7 +14795,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6e01eb8-e70a-4bb7-b0b2-e0191a1d1668}</x14:id>
+          <x14:id>{7ade4ec2-a1bb-408f-9912-c893c8175935}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14789,7 +14807,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e37400a4-b19a-4471-9405-29448db87dca}</x14:id>
+          <x14:id>{bb90f6b2-d085-4350-87dd-e893eabd777c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14826,7 +14844,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a7cf097-df01-4e0b-9c15-a9520084a047}">
+          <x14:cfRule type="dataBar" id="{f8dd37d9-0ad5-43ba-9e35-7d0bb24ed270}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14837,7 +14855,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e089d27f-319d-4e28-bd37-efc0b033cfc7}">
+          <x14:cfRule type="dataBar" id="{b0d436f5-3229-4e8e-a7be-071cc8361450}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14848,14 +14866,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d35d9069-c9a0-4da7-a7c4-419ec500b026}">
+          <x14:cfRule type="dataBar" id="{be026398-f23f-47f9-a85d-b340982e0178}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c2d94e93-1b56-4eb4-9e6f-c33c853e1c77}">
+          <x14:cfRule type="dataBar" id="{029df8e6-0956-4a91-916d-122e5f33b9c3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14866,7 +14884,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{76cdfebc-9db3-482f-bfc3-def288690108}">
+          <x14:cfRule type="dataBar" id="{c8701642-e5a1-406e-ab30-8e7cc02d3054}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14877,7 +14895,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{68b3368b-e8b4-4e26-b354-fd18a580f61e}">
+          <x14:cfRule type="dataBar" id="{26e4c31b-1c51-4349-a562-5d18703bba34}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14888,7 +14906,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b4982086-d8eb-4fc1-997a-d71e5117e6b8}">
+          <x14:cfRule type="dataBar" id="{2c636625-5ee4-48b6-b562-4f7ef85fbce9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14897,7 +14915,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6f0a9c45-c056-4908-adca-b14c586308de}">
+          <x14:cfRule type="dataBar" id="{7a2d6eea-828a-4650-b51d-2f302d9b1a82}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14909,7 +14927,7 @@
           <xm:sqref>AD56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{50fae88e-4780-4f8d-aa46-e4722fe2eb44}">
+          <x14:cfRule type="dataBar" id="{1a52e1de-6eb6-4d70-a9d8-60445feed595}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -14920,7 +14938,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{23f4d11f-2cbc-4ad5-b62b-395942c8602f}">
+          <x14:cfRule type="dataBar" id="{cdd8209b-80ca-4136-a546-4feee398ccf6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14931,14 +14949,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{109d98cd-c981-40c8-b949-0e9f27db7853}">
+          <x14:cfRule type="dataBar" id="{7c9d5dfe-46d7-44a6-b475-56c7fe0ec83b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{049ea757-1ce1-448c-8e67-8fadea3280a7}">
+          <x14:cfRule type="dataBar" id="{d0aa2ba4-66a0-48ae-b2fd-816b297697ae}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14949,7 +14967,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{086827ad-e785-429a-9c71-16a0e77b4030}">
+          <x14:cfRule type="dataBar" id="{5fb1dfb4-d6a7-4d46-bcc8-66d8c0fa52db}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -14960,7 +14978,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f672a979-3f33-4a69-8839-803b11288e7f}">
+          <x14:cfRule type="dataBar" id="{2f3ab93f-1540-436e-a3b5-73313e4187ab}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -14971,7 +14989,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{db06766a-dd6f-4188-98b5-f34a9965f435}">
+          <x14:cfRule type="dataBar" id="{0b904468-8224-4e3e-8598-90264cecb5ce}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14980,7 +14998,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{696e0f09-e970-444c-8e9d-5ff06a6fc217}">
+          <x14:cfRule type="dataBar" id="{3e298ad2-4e9e-4051-b80d-b7396a240037}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -14992,7 +15010,7 @@
           <xm:sqref>K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{95624c8a-c21e-49e8-b505-e960145bfe20}">
+          <x14:cfRule type="dataBar" id="{9aa3e44d-8053-4c56-868c-7f597fb234af}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15003,7 +15021,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4a8cff09-fb14-41ae-9be6-6dcad1c2d62a}">
+          <x14:cfRule type="dataBar" id="{82900eb9-f94f-4a18-b6c2-8bcbc616ae4a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15014,14 +15032,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a662f02d-9568-4431-8220-0777cfe8e2a5}">
+          <x14:cfRule type="dataBar" id="{9bf4d7b7-3db2-4cd9-be29-3d856e10f757}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d399629e-d9bb-4acf-9b9d-9ba683bd366a}">
+          <x14:cfRule type="dataBar" id="{7420a9d9-0f7c-44c3-8a61-0e3e5577ad3e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15032,7 +15050,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0b322cfc-731c-4df8-bc06-58164d180acb}">
+          <x14:cfRule type="dataBar" id="{303ca555-4201-42ed-9633-c7949e4d9294}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15043,7 +15061,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bda07511-7290-4553-bfe2-35056849b2df}">
+          <x14:cfRule type="dataBar" id="{eae7986d-503c-44a8-9171-bc3561b17299}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15054,7 +15072,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b93ffeee-5bf1-421c-838c-bf4de6cece05}">
+          <x14:cfRule type="dataBar" id="{42c6def2-d975-4e92-87ce-58609debe97c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15063,7 +15081,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{35daef96-d3ff-4bc3-bdfc-cd37db7f90a7}">
+          <x14:cfRule type="dataBar" id="{20287a30-46b1-40f1-9081-a6c2a093b1a8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15075,7 +15093,7 @@
           <xm:sqref>AD60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{598d98f2-f70a-48fb-abd2-168da8c2c372}">
+          <x14:cfRule type="dataBar" id="{3202fa0b-f4ed-4171-b289-aec41fe50532}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15086,7 +15104,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1d8dafe6-f99a-47d5-8594-dab72d7ae623}">
+          <x14:cfRule type="dataBar" id="{745b3fb3-b2da-495d-8f07-be9b757cf5fd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15097,14 +15115,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{77e2fc71-0f21-44a1-8646-9d8eee8c22fb}">
+          <x14:cfRule type="dataBar" id="{5e30146e-5cd1-493f-b54e-4e08fbae3eea}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c5e09c52-cd31-4b6e-b1ac-7bb599551704}">
+          <x14:cfRule type="dataBar" id="{aed28516-5b29-4e25-9c92-b3f9b3bc1f6b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15115,7 +15133,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e31f85c0-71c9-40c7-a0b6-cffbeca2087f}">
+          <x14:cfRule type="dataBar" id="{26e679be-149b-402d-934e-64533685dfe4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15126,7 +15144,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c4de0de1-6127-443f-91c1-4a963c37e8ef}">
+          <x14:cfRule type="dataBar" id="{ee212af3-5807-4713-9975-eb8868d806a7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15137,7 +15155,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{563c6788-ec54-4d80-89b9-db9b5080014c}">
+          <x14:cfRule type="dataBar" id="{35e391e1-ccb4-4956-9cfc-d631ef73bd00}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15146,7 +15164,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{595bc562-8d3e-492a-bd31-48e904e64f13}">
+          <x14:cfRule type="dataBar" id="{6913ae6d-44f5-4cc4-842d-9c19918c096f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15158,7 +15176,7 @@
           <xm:sqref>K61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{08ffc4e0-988f-4545-8298-e9161412790a}">
+          <x14:cfRule type="dataBar" id="{1d0afa0a-fca3-4488-a9d4-785e71508049}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15169,7 +15187,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{00563520-ba08-4058-abde-fbb4d465471d}">
+          <x14:cfRule type="dataBar" id="{f75b6ff3-9860-47e5-9d28-080d2b90a20a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15180,14 +15198,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e5e8c13f-273f-4eb2-bc9f-8a941e4e050b}">
+          <x14:cfRule type="dataBar" id="{2ef951a1-581d-459a-b5fc-c25d83f517de}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7d00a515-cb09-40a2-a159-1162f189d47c}">
+          <x14:cfRule type="dataBar" id="{e2c4edd3-dcf1-4010-9994-04ae989354c0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15198,7 +15216,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{24bf41a5-5384-4153-afe5-826e83b25494}">
+          <x14:cfRule type="dataBar" id="{06794649-bf22-42bd-922a-f8a03aefec74}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15209,7 +15227,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{57c411a5-ff59-4789-8ef7-addc0a6ffcea}">
+          <x14:cfRule type="dataBar" id="{ba91d3f2-b574-41df-98db-389b1a4aa89e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15220,7 +15238,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{598c5f0c-a92d-4b1a-ba2c-4176a167d1f9}">
+          <x14:cfRule type="dataBar" id="{7acf6793-72e5-4515-9d50-406fab175039}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15229,7 +15247,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{941d4a85-4a07-43fa-b94c-2e1c676a6a29}">
+          <x14:cfRule type="dataBar" id="{4bd42acc-397b-4f0e-9235-9dab75ccde1b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15241,7 +15259,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{605d2638-6f65-412a-b83b-548ea6e84f99}">
+          <x14:cfRule type="dataBar" id="{61983b95-1bc7-45bf-a7e1-0d77a4be1697}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15252,7 +15270,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8bc4db2c-9bce-4e01-945d-cff136543605}">
+          <x14:cfRule type="dataBar" id="{2256cc2f-038c-4121-8614-58c08f36139a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15263,14 +15281,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{78a77489-9ed9-4049-aa3a-9429d8eda6a5}">
+          <x14:cfRule type="dataBar" id="{0ccfacc4-2e98-4aeb-a8f9-d2e87436df17}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{38f40bb0-97af-4254-904b-0e84e90b512a}">
+          <x14:cfRule type="dataBar" id="{2e9f8857-0abc-4084-af13-fcec883be745}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15281,7 +15299,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{91a93edd-0e7f-4bc0-9c07-a4ba8130d3d4}">
+          <x14:cfRule type="dataBar" id="{2d0bf7fc-46d4-4127-a1c2-289fae48076c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15292,7 +15310,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8de5a738-3150-4715-b673-92c4d3506eaa}">
+          <x14:cfRule type="dataBar" id="{561b35bf-f1ac-4a7d-bca2-203b680b519d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15303,7 +15321,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{02075783-6d6d-457d-bd78-cdebbee61576}">
+          <x14:cfRule type="dataBar" id="{900016d7-d64c-4f8e-bda0-7d9f370628b1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15312,7 +15330,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{30e7bda7-859c-4976-ac8d-f987302bc234}">
+          <x14:cfRule type="dataBar" id="{b7c9ef0f-bf41-4dfb-b749-c2f229d5b122}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15324,7 +15342,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c060139e-4097-4a98-a8a5-979557268789}">
+          <x14:cfRule type="dataBar" id="{613aa387-d0b6-45cb-b3cd-1d9d32ddfd5d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15335,7 +15353,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d976fd5e-551f-4e6d-9144-cf5457170844}">
+          <x14:cfRule type="dataBar" id="{16c7c2d2-7e07-4860-aa0f-0efd88aa3683}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15346,14 +15364,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c99d7190-788d-4273-903f-0714294f3b8b}">
+          <x14:cfRule type="dataBar" id="{53d60f3b-8c98-4283-bb23-3603259cc149}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b457db95-d0de-4c28-8796-38334285842f}">
+          <x14:cfRule type="dataBar" id="{2f104416-c5d5-47bc-ad2f-bf622e99b789}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15364,7 +15382,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{25bdc30b-d4c4-45cf-a2b1-befad951804d}">
+          <x14:cfRule type="dataBar" id="{2beb57a7-a286-4c26-bfeb-66e8108b93c6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15375,7 +15393,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e68fd87a-916a-4d03-8fa7-9cf4cd9755e5}">
+          <x14:cfRule type="dataBar" id="{d54625bc-01b6-4e8f-862e-9be617c7b7ab}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15386,7 +15404,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4a7bd11d-aaff-4668-9029-0762701eca5b}">
+          <x14:cfRule type="dataBar" id="{f89376e1-71a2-45df-b009-60b6b96f1f50}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15395,7 +15413,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5b3f4be2-0197-466a-ab01-c04b8792ec8b}">
+          <x14:cfRule type="dataBar" id="{e1c1f213-9562-492f-849e-236a6fbd0afe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15407,7 +15425,7 @@
           <xm:sqref>K57:K58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a9a8bf0-2cb3-4057-af38-bebd480260ae}">
+          <x14:cfRule type="dataBar" id="{bd660bf2-c44c-4355-8b61-67fd74d67f4d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15419,7 +15437,7 @@
           <xm:sqref>K187:K206</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a8dce3a7-ee08-4a34-9ac1-8f9e673ba224}">
+          <x14:cfRule type="dataBar" id="{d7b01846-ff5f-481e-94e6-fb0a080b2058}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15431,7 +15449,7 @@
           <xm:sqref>AD56:AE57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9780f81e-354d-44eb-9157-f708e85c65e0}">
+          <x14:cfRule type="dataBar" id="{00eb0ea0-78b5-4e5d-b53c-76495df8839b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15443,7 +15461,7 @@
           <xm:sqref>AD60:AE63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3f60dffe-320c-457c-b5e1-222aae6f870b}">
+          <x14:cfRule type="dataBar" id="{6550637d-847b-4599-9131-1762b5cb3de1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -15454,7 +15472,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5323ee68-9b71-4f5a-9843-9ff32b9eb99c}">
+          <x14:cfRule type="dataBar" id="{8427225c-5b24-4584-bfd1-e11d4fccbedd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15465,14 +15483,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9c1144dc-f6b5-4acb-8e24-d67cd9b6a9e4}">
+          <x14:cfRule type="dataBar" id="{9654132b-b282-4a5b-a230-f7208da4e900}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ceeb4f2f-567b-4d52-8441-1ec014249014}">
+          <x14:cfRule type="dataBar" id="{933bdeb4-44f9-44cf-ab09-b6005fc7e759}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15483,7 +15501,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0cebd8f3-72d0-4661-82fe-75a26b6013f9}">
+          <x14:cfRule type="dataBar" id="{3a53b751-6b45-49a0-9e96-936c8e27db7e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -15494,7 +15512,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6d2724b8-3cb2-48c5-9699-8bce34f2cedf}">
+          <x14:cfRule type="dataBar" id="{4106a878-16bf-48eb-8b3b-0972440acf08}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -15505,7 +15523,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a168e323-b733-44e6-826c-bf7b0571002a}">
+          <x14:cfRule type="dataBar" id="{fb538c8a-81d7-4e6a-b8ad-bc38c7f210b0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15514,7 +15532,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0542ffd4-fc81-4605-99f1-6944753e696a}">
+          <x14:cfRule type="dataBar" id="{2d8862f3-0d74-4922-bb60-d1d261292f08}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15526,7 +15544,7 @@
           <xm:sqref>F67 F77 F87 F97 F107 F117 F127 F137 F147 F157 F167 F177</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ab77f350-c989-419e-970a-228d838e70a5}">
+          <x14:cfRule type="dataBar" id="{1c19f651-ee91-4534-98cb-c3b3b089846e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15535,7 +15553,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8e37c347-0c52-4517-a794-b5b0da5b3255}">
+          <x14:cfRule type="dataBar" id="{4d636ca4-5be8-423d-b0b9-435b8e2c8b3a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15547,7 +15565,7 @@
           <xm:sqref>K67:K77 K83:K97 K103:K117 K123:K137 K143:K157 K163:K177 K183:K186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ce86388-d070-4721-9114-b6f67df5a7cc}">
+          <x14:cfRule type="dataBar" id="{1720642c-3530-4294-b7a2-ef11d2537329}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15559,7 +15577,7 @@
           <xm:sqref>Y67:Y77 Y83:Y97 Y103:Y120 Y123:Y139 Y143:Y158 Y163:Y177 Y183:Y186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{932afb0c-44af-453d-b841-9bb36363ab9e}">
+          <x14:cfRule type="dataBar" id="{c64afc50-7e6a-4843-84c9-f4849e154217}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15568,7 +15586,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0bf539db-74d2-494e-9386-ccaa3e813c24}">
+          <x14:cfRule type="dataBar" id="{03801493-5bcb-47a5-bddc-85d8a7a74842}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15580,14 +15598,14 @@
           <xm:sqref>AB67 AB87 AB107 AB127 AB147 AB167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a9621808-fad4-4e6d-a303-6495c0ac0736}">
+          <x14:cfRule type="dataBar" id="{6e051b41-a042-40ef-a400-0d4fddd228d2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{38c3df44-ab19-4d88-9bf6-c328ea9f830b}">
+          <x14:cfRule type="dataBar" id="{e684fbb5-17d2-4457-a3ae-6558557579ab}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15599,7 +15617,7 @@
           <xm:sqref>AB67:AB77 AB83:AB97 AB103:AB120 AB123:AB139 AB143:AB158 AB163:AB177 AB183:AB186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b68a37ab-e99b-4017-ac20-089d85f9fe13}">
+          <x14:cfRule type="dataBar" id="{42403239-53de-48af-a42d-aa64ebacf436}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15611,7 +15629,7 @@
           <xm:sqref>AB67:AB77 AB83:AB97 AB103:AB117 AB123:AB137 AB143:AB157 AB163:AB177 AB183:AB186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1fbd06b1-8b44-4327-8ab8-aee20e156610}">
+          <x14:cfRule type="dataBar" id="{742bfa9f-9d44-43dd-b116-ed385c276ca6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15620,7 +15638,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ca2b57c7-7278-4369-adb3-09056b9e097b}">
+          <x14:cfRule type="dataBar" id="{4996df7b-5f2d-4074-8b41-77825d0712d0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15632,7 +15650,7 @@
           <xm:sqref>K78:K82 K98:K102 K118:K122 K138:K142 K158:K162 K178:K182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8aea28ba-1af0-4071-8f76-2e6af242d094}">
+          <x14:cfRule type="dataBar" id="{d9a26976-b2ba-49d8-8b04-d1fcac6ff96b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15644,14 +15662,14 @@
           <xm:sqref>Y78:Y82 Y98:Y102 Y118:Y122 Y138:Y142 Y158:Y162 Y178:Y182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38c53682-7597-4f43-8647-7d64657c6e15}">
+          <x14:cfRule type="dataBar" id="{48c576ba-f0fd-4b5c-b49d-b2c3f93b50e3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{91b3922e-0b32-4e30-a97a-cf1bc03a31e0}">
+          <x14:cfRule type="dataBar" id="{6938760b-39c8-44e2-8b84-d6851891aaff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15660,7 +15678,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2ed537be-4162-44d1-95bb-bd6cddf59bf9}">
+          <x14:cfRule type="dataBar" id="{cf8b3961-3bfa-4122-9fb2-16b5899749d5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15672,7 +15690,7 @@
           <xm:sqref>AB78:AB82 AB98:AB102 AB118:AB122 AB138:AB142 AB158:AB162 AB178:AB182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9f174a21-7a40-4d20-9a6e-2b2aa049a29f}">
+          <x14:cfRule type="dataBar" id="{8cfe7356-68c5-4e73-b277-efd491d8053d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15681,7 +15699,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6bf99c71-fda8-48e0-84a1-f8f9028430a1}">
+          <x14:cfRule type="dataBar" id="{89675322-6524-47bc-8883-30daea2addbe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15690,7 +15708,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{39476877-9ea9-4f8c-bb85-d64ed872b47e}">
+          <x14:cfRule type="dataBar" id="{62b2b25e-fc64-4ae1-ba88-6127f2947d66}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15702,7 +15720,7 @@
           <xm:sqref>F187 F192 F197 F202</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d6e01eb8-e70a-4bb7-b0b2-e0191a1d1668}">
+          <x14:cfRule type="dataBar" id="{7ade4ec2-a1bb-408f-9912-c893c8175935}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15711,7 +15729,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e37400a4-b19a-4471-9405-29448db87dca}">
+          <x14:cfRule type="dataBar" id="{bb90f6b2-d085-4350-87dd-e893eabd777c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -15732,12 +15750,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
